--- a/digital-products/hdb-tenant-pack/singapore-hdb-tenant-protection-cost-pack-2026.xlsx
+++ b/digital-products/hdb-tenant-pack/singapore-hdb-tenant-protection-cost-pack-2026.xlsx
@@ -93,7 +93,7 @@
     <t>The calculator works entirely offline inside this file. It never fetches live rental or utility data.</t>
   </si>
   <si>
-    <t>Stamp duty calculations follow IRAS guidelines for lease agreements. Verify current rates on IRAS website before relying on them.</t>
+    <t>Stamp duty calculations follow IRAS guidelines for lease agreements. For a tenancy agreement, the tenant/lessee is generally liable for lease duty unless the agreement states otherwise. Verify current rates on IRAS website before relying on them.</t>
   </si>
   <si>
     <t>This pack is a practical planning tool. It is NOT legal advice. For legal questions, consult a qualified professional.</t>
@@ -174,10 +174,10 @@
     <t>Typically 1–2 months. Enter number of months; formula converts to S$.</t>
   </si>
   <si>
-    <t>Stamp duty (tenant's share)</t>
-  </si>
-  <si>
-    <t>Lease duty per IRAS. For leases ≤3 years: 0.4% of total rent. Verify on IRAS website.</t>
+    <t>Stamp duty (tenant's share per agreement)</t>
+  </si>
+  <si>
+    <t>Lease duty per IRAS. For leases ≤3 years: 0.4% of total rent. For a tenancy agreement, the tenant/lessee is generally liable for lease duty unless the agreement states otherwise. Verify on IRAS website.</t>
   </si>
   <si>
     <t>Agent commission (if any)</t>
@@ -432,7 +432,7 @@
     <t>Utility bills: whose name? How reimbursed?</t>
   </si>
   <si>
-    <t>Stamp duty: who pays? Tenant's share per IRAS?</t>
+    <t>Stamp duty: who pays per agreement? Tenant/lessee generally liable unless TA states otherwise</t>
   </si>
   <si>
     <t>DOCUMENTATION &amp; EVIDENCE</t>
@@ -579,7 +579,7 @@
     <t>Agent commission receipt (if paid)</t>
   </si>
   <si>
-    <t>Stamp duty: tenant's share calculated, payment plan agreed</t>
+    <t>Stamp duty: liability per agreement (tenant/lessee generally liable unless TA states otherwise), payment plan agreed</t>
   </si>
   <si>
     <t>Post-dated cheques / GIRO / standing instruction details confirmed</t>
@@ -591,7 +591,7 @@
     <t>Lease duty calculated per IRAS: 0.4% of total rent for lease ≤3 years (tenant's share)</t>
   </si>
   <si>
-    <t>Stamp duty paid within 14 days of signing (penalty if late)</t>
+    <t>Stamp duty paid within 14 days of signing (penalty if late) — liability per agreement</t>
   </si>
   <si>
     <t>e-Stamping via IRAS portal (www.iras.gov.sg) — keep certificate</t>
@@ -658,7 +658,7 @@
 • Any other recurring fees (e.g., management fees, parking, dryer usage)
 Also, please confirm:
 • Security deposit: [X] months = S$[amount]
-• Stamp duty: tenant's share per IRAS guidelines — who will handle e-stamping?
+• Stamp duty: liability per agreement (tenant/lessee generally liable per IRAS unless TA states otherwise) — who will handle e-stamping?
 • Agent commission (if any): amount and payer
 Thank you,
 [Your Name]</t>
@@ -708,7 +708,7 @@
   - To be held by: [stakeholder / joint account / lawyer / landlord]
   - Receipt to be issued upon receipt
 • First month rent: S$[amount] due on move-in [date]
-• Stamp duty (tenant's share per IRAS): S$[amount] — to be e-stamped by [landlord/agent/me] within 14 days
+• Stamp duty (tenant/lessee generally liable per IRAS unless TA states otherwise): S$[amount] — to be e-stamped by [landlord/agent/me] within 14 days
 • Agent commission (if any): S$[amount] payable by [tenant/landlord]
 • Lease term: [X] months, from [start date] to [end date]
 • Notice period: [X] months
@@ -784,7 +784,7 @@
     <t>Key Assumptions in This Pack</t>
   </si>
   <si>
-    <t>• Stamp duty calculated at 0.4% of total rent (lease ≤ 3 years). Verify current rate on IRAS website.</t>
+    <t>• Stamp duty calculated at 0.4% of total rent (lease ≤ 3 years). For a tenancy agreement, the tenant/lessee is generally liable for lease duty unless the agreement states otherwise. Verify current rate on IRAS website.</t>
   </si>
   <si>
     <t>• Security deposit: 1–2 months rent is market practice; HDB does not mandate a specific amount.</t>
